--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3235,6 +3235,112 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121659150</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57725</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 54601, Brotorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>575628</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6404582</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -3240,7 +3240,7 @@
         <v>121659150</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>57726</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -3240,7 +3240,7 @@
         <v>121659150</v>
       </c>
       <c r="B23" t="n">
-        <v>57726</v>
+        <v>57734</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -2527,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">

--- a/artfynd/A 54601-2022 artfynd.xlsx
+++ b/artfynd/A 54601-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91218403</v>
+        <v>96556999</v>
       </c>
       <c r="B2" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hummelstad, Brotorp, Sm</t>
+          <t>Brotorpsskogen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575762.793676891</v>
+        <v>575682</v>
       </c>
       <c r="R2" t="n">
-        <v>6404599.94677332</v>
+        <v>6404524</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-02-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-02-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Intensivt trummande i dungen morg/fm</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,44 +782,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91774603</v>
+        <v>97700240</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -842,27 +822,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hummelstad, Brotorp, Sm</t>
+          <t>Brotorpsskogen, Hummelstad, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575762.793676891</v>
+        <v>575780</v>
       </c>
       <c r="R3" t="n">
-        <v>6404599.94677332</v>
+        <v>6404610</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-03-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,6 +879,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -928,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94235956</v>
+        <v>105804970</v>
       </c>
       <c r="B4" t="n">
-        <v>39527</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,54 +909,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101060</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svävflugedagsvärmare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hemaris tityus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hummelstad, Brotorp, Sm</t>
+          <t>A 54601, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575762.793676891</v>
+        <v>575628</v>
       </c>
       <c r="R4" t="n">
-        <v>6404599.94677332</v>
+        <v>6404582</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,27 +970,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tjärblomster.</t>
+          <t>På undersidan/sidan av granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,49 +1001,44 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96263359</v>
+        <v>111837758</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2014</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1110,14 +1050,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Brotorp S, Hummelstad, Sm</t>
+          <t>Brotorp, hyggeskant, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575779.7083346407</v>
+        <v>575674</v>
       </c>
       <c r="R5" t="n">
-        <v>6404609.866083559</v>
+        <v>6404513</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,27 +1084,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>50+30 fruktkroppar vid två tallar.</t>
+          <t>På asplåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1192,42 +1122,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96263315</v>
+        <v>111837741</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1239,14 +1164,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brotorp S, Hummelstad, Sm</t>
+          <t>Brotorp, hyggeskant, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575746.1670393839</v>
+        <v>575654</v>
       </c>
       <c r="R6" t="n">
-        <v>6404546.29432008</v>
+        <v>6404507</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,22 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,42 +1231,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96556999</v>
+        <v>111837705</v>
       </c>
       <c r="B7" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>366</v>
+        <v>4363</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1363,14 +1273,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Sm</t>
+          <t>Brotorp, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575682.4597875664</v>
+        <v>575795</v>
       </c>
       <c r="R7" t="n">
-        <v>6404523.760571928</v>
+        <v>6404519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,34 +1307,19 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
@@ -1445,42 +1340,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96557108</v>
+        <v>96263359</v>
       </c>
       <c r="B8" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1492,14 +1382,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Sm</t>
+          <t>Brotorp S, Hummelstad, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575771.2760228274</v>
+        <v>575780</v>
       </c>
       <c r="R8" t="n">
-        <v>6404546.766638689</v>
+        <v>6404610</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1526,22 +1416,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>50+30 fruktkroppar vid två tallar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,16 +1467,11 @@
         <v>96557117</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1620,10 +1510,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575771.2760228274</v>
+        <v>575771</v>
       </c>
       <c r="R9" t="n">
-        <v>6404546.766638689</v>
+        <v>6404547</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1653,19 +1543,9 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1693,42 +1573,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97700240</v>
+        <v>112360057</v>
       </c>
       <c r="B10" t="n">
-        <v>89390</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1110</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1740,14 +1615,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Hummelstad, Sm</t>
+          <t>Brotorp, Hummelstad, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575779.7083346407</v>
+        <v>575771</v>
       </c>
       <c r="R10" t="n">
-        <v>6404609.866083559</v>
+        <v>6404602</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1774,22 +1649,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1817,37 +1682,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97695128</v>
+        <v>105344960</v>
       </c>
       <c r="B11" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>4660</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1855,24 +1715,23 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Sm</t>
+          <t>A 54601, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575761.6122784532</v>
+        <v>575585</v>
       </c>
       <c r="R11" t="n">
-        <v>6404577.521955938</v>
+        <v>6404590</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1899,22 +1758,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-12-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På liggande död asp.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1923,6 +1777,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1941,15 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97964712</v>
+        <v>96263315</v>
       </c>
       <c r="B12" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1957,46 +1807,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100067</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brotorpsskogen, Sm</t>
+          <t>Brotorp S, Hummelstad, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575682.4597875664</v>
+        <v>575746</v>
       </c>
       <c r="R12" t="n">
-        <v>6404523.760571928</v>
+        <v>6404546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2023,22 +1872,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-01-07</t>
+          <t>2021-09-23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2047,6 +1896,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2065,37 +1915,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105344960</v>
+        <v>96557108</v>
       </c>
       <c r="B13" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4660</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2105,21 +1950,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 54601, Brotorp, Sm</t>
+          <t>Brotorpsskogen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575585.0262648202</v>
+        <v>575771</v>
       </c>
       <c r="R13" t="n">
-        <v>6404589.672404896</v>
+        <v>6404547</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2146,27 +1991,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-12-25</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-12-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På liggande död asp.</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2194,60 +2024,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105804970</v>
+        <v>91774594</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100038</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 54601, Brotorp, Sm</t>
+          <t>Hummelstad, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575627.9246910355</v>
+        <v>575763</v>
       </c>
       <c r="R14" t="n">
-        <v>6404581.943433098</v>
+        <v>6404600</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2271,27 +2101,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-01-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-01-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På undersidan/sidan av granlåga</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2300,7 +2115,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2312,72 +2126,67 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111837675</v>
+        <v>91218403</v>
       </c>
       <c r="B15" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Brotorp, Långsjön, Sm</t>
+          <t>Hummelstad, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575782</v>
+        <v>575763</v>
       </c>
       <c r="R15" t="n">
-        <v>6404547</v>
+        <v>6404600</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2401,12 +2210,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-02-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-02-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Intensivt trummande i dungen morg/fm</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2415,7 +2229,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2427,22 +2240,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111837705</v>
+        <v>91774603</v>
       </c>
       <c r="B16" t="n">
-        <v>90662</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2450,48 +2258,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4363</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brotorp, Långsjön, Sm</t>
+          <t>Hummelstad, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575795</v>
+        <v>575763</v>
       </c>
       <c r="R16" t="n">
-        <v>6404519</v>
+        <v>6404600</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2515,21 +2324,20 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-03-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2548,61 +2356,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111837758</v>
+        <v>97695128</v>
       </c>
       <c r="B17" t="n">
-        <v>90187</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2014</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Brotorp, hyggeskant, Sm</t>
+          <t>Brotorpsskogen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575674</v>
+        <v>575762</v>
       </c>
       <c r="R17" t="n">
-        <v>6404513</v>
+        <v>6404578</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2629,17 +2433,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På asplåga.</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2648,7 +2447,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2667,61 +2465,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111837741</v>
+        <v>97964712</v>
       </c>
       <c r="B18" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>100067</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brotorp, hyggeskant, Sm</t>
+          <t>Brotorpsskogen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575654</v>
+        <v>575682</v>
       </c>
       <c r="R18" t="n">
-        <v>6404507</v>
+        <v>6404524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2748,12 +2542,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2762,7 +2556,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2781,15 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112360063</v>
+        <v>94255908</v>
       </c>
       <c r="B19" t="n">
-        <v>90899</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57942</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2797,48 +2585,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>102119</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brotorp, Hummelstad, Sm</t>
+          <t>Hummelstad, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575771</v>
+        <v>575763</v>
       </c>
       <c r="R19" t="n">
-        <v>6404602</v>
+        <v>6404600</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2862,12 +2651,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2021-06-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2021-06-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>02:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2876,7 +2675,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2895,15 +2693,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112360070</v>
+        <v>121659150</v>
       </c>
       <c r="B20" t="n">
-        <v>103842</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,42 +2704,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brotorp, Hummelstad, Sm</t>
+          <t>A 54601, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575771</v>
+        <v>575628</v>
       </c>
       <c r="R20" t="n">
-        <v>6404602</v>
+        <v>6404582</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2973,17 +2762,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Få</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2992,7 +2776,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3011,15 +2794,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112360057</v>
+        <v>116466731</v>
       </c>
       <c r="B21" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,45 +2805,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>208255</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brotorp, Hummelstad, Sm</t>
+          <t>A 54601, Brotorp, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575771</v>
+        <v>575628</v>
       </c>
       <c r="R21" t="n">
-        <v>6404602</v>
+        <v>6404582</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3092,12 +2868,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3125,15 +2901,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116466731</v>
+        <v>111837675</v>
       </c>
       <c r="B22" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3141,43 +2912,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208255</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 54601, Brotorp, Sm</t>
+          <t>Brotorp, Långsjön, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575628</v>
+        <v>575782</v>
       </c>
       <c r="R22" t="n">
-        <v>6404582</v>
+        <v>6404547</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3204,12 +2978,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3237,15 +3011,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121659150</v>
+        <v>112360070</v>
       </c>
       <c r="B23" t="n">
-        <v>57734</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3253,38 +3022,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 54601, Brotorp, Sm</t>
+          <t>Brotorp, Hummelstad, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575628</v>
+        <v>575771</v>
       </c>
       <c r="R23" t="n">
-        <v>6404582</v>
+        <v>6404602</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3311,12 +3084,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Få</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3325,6 +3103,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3340,6 +3119,117 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>116468450</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brotorp, Hummelstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>575599</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6404549</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Få, igenväxande beteshage. På samma ställe där slåttergubbe växte för många år sedan-</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
